--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N107_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N107_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>36.95809225165755</v>
+        <v>6.005689990894352</v>
       </c>
       <c r="D2" t="n">
-        <v>36.83374862000266</v>
+        <v>5.985484150750432</v>
       </c>
       <c r="E2" t="n">
-        <v>15.93794147033692</v>
+        <v>2.58991548892975</v>
       </c>
       <c r="F2" t="n">
-        <v>15.82506024658312</v>
+        <v>2.571572290069757</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>50.72739703537552</v>
+        <v>8.243202018248523</v>
       </c>
       <c r="D3" t="n">
-        <v>50.61325148380681</v>
+        <v>8.224653366118607</v>
       </c>
       <c r="E3" t="n">
-        <v>15.93794147033692</v>
+        <v>2.58991548892975</v>
       </c>
       <c r="F3" t="n">
-        <v>15.82506024658312</v>
+        <v>2.571572290069757</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>35.71833683438413</v>
+        <v>5.804229735587422</v>
       </c>
       <c r="D4" t="n">
-        <v>36.35233067540106</v>
+        <v>5.907253734752673</v>
       </c>
       <c r="E4" t="n">
-        <v>15.93794147033692</v>
+        <v>2.58991548892975</v>
       </c>
       <c r="F4" t="n">
-        <v>15.82506024658312</v>
+        <v>2.571572290069757</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>43.68000182471435</v>
+        <v>7.098000296516082</v>
       </c>
       <c r="D5" t="n">
-        <v>44.31242615327831</v>
+        <v>7.200769249907726</v>
       </c>
       <c r="E5" t="n">
-        <v>15.93794147033692</v>
+        <v>2.58991548892975</v>
       </c>
       <c r="F5" t="n">
-        <v>15.82506024658312</v>
+        <v>2.571572290069757</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>52.04804897139419</v>
+        <v>8.457807957851557</v>
       </c>
       <c r="D6" t="n">
-        <v>51.80757111516885</v>
+        <v>8.418730306214938</v>
       </c>
       <c r="E6" t="n">
-        <v>15.93794147033692</v>
+        <v>2.58991548892975</v>
       </c>
       <c r="F6" t="n">
-        <v>15.82506024658312</v>
+        <v>2.571572290069757</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>55.12891909803201</v>
+        <v>8.958449353430202</v>
       </c>
       <c r="D7" t="n">
-        <v>54.91424562851437</v>
+        <v>8.923564914633586</v>
       </c>
       <c r="E7" t="n">
-        <v>15.93794147033692</v>
+        <v>2.58991548892975</v>
       </c>
       <c r="F7" t="n">
-        <v>15.82506024658312</v>
+        <v>2.571572290069757</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>52.74192674931356</v>
+        <v>8.570563096763454</v>
       </c>
       <c r="D8" t="n">
-        <v>52.1088961241011</v>
+        <v>8.467695620166429</v>
       </c>
       <c r="E8" t="n">
-        <v>15.93794147033692</v>
+        <v>2.58991548892975</v>
       </c>
       <c r="F8" t="n">
-        <v>15.82506024658312</v>
+        <v>2.571572290069757</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>32.93119135917191</v>
+        <v>5.351318595865436</v>
       </c>
       <c r="D9" t="n">
-        <v>33.45332832410033</v>
+        <v>5.436165852666305</v>
       </c>
       <c r="E9" t="n">
-        <v>15.93794147033692</v>
+        <v>2.58991548892975</v>
       </c>
       <c r="F9" t="n">
-        <v>15.82506024658312</v>
+        <v>2.571572290069757</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>7.207638265516558</v>
+        <v>1.171241218146441</v>
       </c>
       <c r="D10" t="n">
-        <v>7.867496865281088</v>
+        <v>1.278468240608177</v>
       </c>
       <c r="E10" t="n">
-        <v>15.93794147033692</v>
+        <v>2.58991548892975</v>
       </c>
       <c r="F10" t="n">
-        <v>15.82506024658312</v>
+        <v>2.571572290069757</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>12.35374637507521</v>
+        <v>2.007483785949721</v>
       </c>
       <c r="D11" t="n">
-        <v>11.60171021817479</v>
+        <v>1.885277910453404</v>
       </c>
       <c r="E11" t="n">
-        <v>15.93794147033692</v>
+        <v>2.58991548892975</v>
       </c>
       <c r="F11" t="n">
-        <v>15.82506024658312</v>
+        <v>2.571572290069757</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
